--- a/RotatingDrive/RotatingDrive.xlsx
+++ b/RotatingDrive/RotatingDrive.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-RotatingDrive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B262CA7-7027-4F01-B184-47EED93EA774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636BE05C-EC73-482E-A2E1-527A8A787972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2010" windowWidth="21600" windowHeight="11295" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
+    <workbookView xWindow="1425" yWindow="2565" windowWidth="25170" windowHeight="11295" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Rotating-Drive" sheetId="1" r:id="rId1"/>
+    <sheet name="BOM Rotating Drive" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="129">
   <si>
     <t>RD020</t>
   </si>
@@ -68,93 +69,372 @@
     <t>RD013</t>
   </si>
   <si>
-    <t>When installed on NFSROBOT, need to calibrate and test &gt; C024</t>
-  </si>
-  <si>
     <t>RD012</t>
+  </si>
+  <si>
+    <t>RD011</t>
+  </si>
+  <si>
+    <t>Also a platform or rig is needed to guide the cable-chain spiral. For now 2 rigs are used.</t>
+  </si>
+  <si>
+    <t>RD010</t>
+  </si>
+  <si>
+    <t>RD009</t>
+  </si>
+  <si>
+    <t>The casing of the drive is also needed for supporting the cable spiral coming from the arm -assy and going into the foot. Checklist C013 
+I added 2 supports  angled 45 degrees from central axis and on one support an endplate to block the cable-chain from moving too much.  So far this works fine.</t>
+  </si>
+  <si>
+    <t>RD008</t>
+  </si>
+  <si>
+    <t>For the drive to calculate the needed torque and speed/accel the formulation to be adapted. I have no feeling yet with the steppermotor behaviour incombination with GRBL settings. Checklist C007 For now i just use one of the strongest Nema17 size motor and a 10:1 reduction gear. 
+It works very well!!</t>
+  </si>
+  <si>
+    <t>RD007</t>
+  </si>
+  <si>
+    <t>The connection of the PHI-rotator on the tripod enhanced to be rocksolid stiff connected to tripod, including leaving room for fastening knob of tripod. Checklist C003, Done.</t>
+  </si>
+  <si>
+    <t>RD006</t>
+  </si>
+  <si>
+    <t>Another issue is that all the belt lenth calculators i could access on the internet gave wrong results, very curious.  But it means i have to device a calculator in Fusion 360 to satisfy the need. Checklist C004. Stopped, the https://www.dold-mechatronik.de/Zahnriemen  provides a close enough ressult.</t>
+  </si>
+  <si>
+    <t>RD005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yet the proto also showed the need to control the belt tension as a rocking motion at start en stop of a step is direct result of not tight belt tensioning. So checklist C003. Done. </t>
+  </si>
+  <si>
+    <t>RD004</t>
+  </si>
+  <si>
+    <t>So a second proto made and this one did rotate the test arm in a controllable way up to ~1 degree steps.  Use of a reduction gearing of 10:1 plus HTD3M toothed belt and a 270:20 pulley ratio. Thus 135:1. With appropriate GRBL settings for acceleration and speed a 1 degree step is possible and a 180 degree sweep in ~ 9 seconds. Checklist C002, Done.</t>
+  </si>
+  <si>
+    <t>RD003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So i made a proto and found that probable the reduction was not great enough for the motor used. </t>
+  </si>
+  <si>
+    <t>RD002</t>
+  </si>
+  <si>
+    <t>The rotating drive is the most difficult for me to determine the right motor reduction and sizing of belt etc on beforehand. Basically because i have little understanding of the stepper motor behaviour.</t>
+  </si>
+  <si>
+    <t>RD001</t>
+  </si>
+  <si>
+    <t>Decisions</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Part ID</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Buy/Make</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Buy</t>
+  </si>
+  <si>
+    <t>Make</t>
+  </si>
+  <si>
+    <t>3D printed, using PETG (Rapid PETG)</t>
+  </si>
+  <si>
+    <t>BOM for the HALS-Mechatronics Rotating Drive</t>
+  </si>
+  <si>
+    <t>RD-TS001</t>
+  </si>
+  <si>
+    <t>RotatingDrive-Tensioner-System</t>
+  </si>
+  <si>
+    <t>RD-TS002</t>
+  </si>
+  <si>
+    <t>RD-TS003</t>
+  </si>
+  <si>
+    <t>RD-TS004</t>
+  </si>
+  <si>
+    <t>RD-TS005</t>
+  </si>
+  <si>
+    <t>RD-TS006</t>
+  </si>
+  <si>
+    <t>Tension roller-guide</t>
+  </si>
+  <si>
+    <t>Tension roller-frame</t>
+  </si>
+  <si>
+    <t>Flange bearing-8x16x5mm</t>
+  </si>
+  <si>
+    <t>Bearing-8x16x5mm</t>
+  </si>
+  <si>
+    <t>Axle-H7-8mmx28mm</t>
+  </si>
+  <si>
+    <t>Typically sold as a bar, some suppliers provide cut to size as option.</t>
+  </si>
+  <si>
+    <t>Bolt M8x35mm</t>
+  </si>
+  <si>
+    <t>To bolt down the tension roller-frame.</t>
+  </si>
+  <si>
+    <t>RD-TS007</t>
+  </si>
+  <si>
+    <t>A flat-head bolt with allen key slot. Its use is to adjust the motor-pulley-assy alignment.</t>
+  </si>
+  <si>
+    <t>RotatingDrive-Motor-Pulley-Assy</t>
+  </si>
+  <si>
+    <t>RD-MP001</t>
+  </si>
+  <si>
+    <t>MotorMount-01</t>
+  </si>
+  <si>
+    <t>MotorMount-filling plate-1mm</t>
+  </si>
+  <si>
+    <t>If needed, and this can be of rubber</t>
+  </si>
+  <si>
+    <t>RD-MP002</t>
+  </si>
+  <si>
+    <t>RD-MP003</t>
+  </si>
+  <si>
+    <t>RD-MP004</t>
+  </si>
+  <si>
+    <t>Axle-H7-8mmx65mm</t>
+  </si>
+  <si>
+    <t>https://www.omc-stepperonline.com/</t>
+  </si>
+  <si>
+    <t>Stepper motor 17HE24-2104S</t>
+  </si>
+  <si>
+    <t>M4x16 allen screw plus washer</t>
+  </si>
+  <si>
+    <t>to mount motor-reductiongear assy</t>
+  </si>
+  <si>
+    <t>RD-MP005</t>
+  </si>
+  <si>
+    <t>RD-MP006</t>
+  </si>
+  <si>
+    <t>RD-MP007</t>
+  </si>
+  <si>
+    <t>RD-MP008</t>
+  </si>
+  <si>
+    <t>https://www.dold-mechatronik.de/</t>
+  </si>
+  <si>
+    <t>https://www.systeal.com      reference: VIS-XP-CBM5-15</t>
+  </si>
+  <si>
+    <t>HTD3M 9mm 20t pulley 8mm axle</t>
+  </si>
+  <si>
+    <t>Reduction gear EG17-G10</t>
+  </si>
+  <si>
+    <t>RD-MP009</t>
+  </si>
+  <si>
+    <t>MH2025-8-8-ElastFlexCoupling</t>
+  </si>
+  <si>
+    <t>RD-MP010</t>
+  </si>
+  <si>
+    <t>RD-CH001</t>
+  </si>
+  <si>
+    <t>Specific for the gravity tripod, using 3d Model: TripodCentralMount-Replica</t>
+  </si>
+  <si>
+    <t>RD-CH002</t>
+  </si>
+  <si>
+    <t>RD-CH003</t>
+  </si>
+  <si>
+    <t>Main chassis beam</t>
+  </si>
+  <si>
+    <t>CableChain-mount- Chassis-side</t>
+  </si>
+  <si>
+    <t>specific for the closed belt size HTD3M-1068mm ; 3D printed, using PETG (Rapid PETG)</t>
+  </si>
+  <si>
+    <t>3D printed, using PETG (Rapid PETG), glued to chassis beam with cyanoacrylarte (degrease first!)</t>
+  </si>
+  <si>
+    <t>Cable-Clamp-03</t>
+  </si>
+  <si>
+    <t>RD-CH004</t>
+  </si>
+  <si>
+    <t>Cablechain-L-support Part-1</t>
+  </si>
+  <si>
+    <t>Cablechain-R-support Part-1</t>
+  </si>
+  <si>
+    <t>Cablechain-Support-Part-2</t>
+  </si>
+  <si>
+    <t>Cablechain-Stop</t>
+  </si>
+  <si>
+    <t>RD-CH005</t>
+  </si>
+  <si>
+    <t>RD-CH006</t>
+  </si>
+  <si>
+    <t>RD-CH007</t>
+  </si>
+  <si>
+    <t>RD-CH008</t>
+  </si>
+  <si>
+    <t>3D printed, using PETG (Rapid PETG), glued to support (degrease first!)</t>
+  </si>
+  <si>
+    <t>3D printed, using PETG (Rapid PETG), glued to end of Part-2 (degrease first!)</t>
+  </si>
+  <si>
+    <t>3D printed, using PETG (Rapid PETG), glued to main pulley (degrease first!)</t>
+  </si>
+  <si>
+    <t>RD-CH009</t>
+  </si>
+  <si>
+    <t>Mswitch-bracket</t>
+  </si>
+  <si>
+    <t>Mswitch-bracket-Clamp</t>
+  </si>
+  <si>
+    <t>RD-CH010</t>
+  </si>
+  <si>
+    <t>RD-CH011</t>
+  </si>
+  <si>
+    <t>HUB as Central part to fit on tripod mount</t>
+  </si>
+  <si>
+    <t>RotatingDrive-CHASSIS</t>
+  </si>
+  <si>
+    <t>Swich triangle to trigger endstop switch</t>
+  </si>
+  <si>
+    <t>RD-CH012</t>
+  </si>
+  <si>
+    <t>M3x20 bolt + nut</t>
+  </si>
+  <si>
+    <t>Flathead-bolt-M5x12mm  (www.systeal.com)</t>
+  </si>
+  <si>
+    <t>Flathead-bolt-M5x15mm (www.systeal.com)</t>
+  </si>
+  <si>
+    <t>For M5 and M8 bolts the holes are tapped , use a bit of isopropyl-alcohol to reduce friction and temperature raising. Practice this before final.</t>
+  </si>
+  <si>
+    <t>The Nema17 motor cable connection requires an endcap to secure the cable mount to the motor.</t>
+  </si>
+  <si>
+    <t>RD-MP011</t>
+  </si>
+  <si>
+    <t>NEMA17-ENDCAP-CABLING</t>
+  </si>
+  <si>
+    <t>RotatingDrive-Main-Pulley</t>
+  </si>
+  <si>
+    <t>Main pulley HTD3M-9mm-270t</t>
+  </si>
+  <si>
+    <t>3D printed, using PETG (Rapid PETG). ! Make sure the dimensional correctness of your printer!</t>
+  </si>
+  <si>
+    <t>Bearing 65x50x7mm 6810-2RS</t>
+  </si>
+  <si>
+    <t>Must fit thightly in main pulley and on HUB</t>
+  </si>
+  <si>
+    <t>The chassis as it is now suffices for the first working version of NFSROBOT. But will be replaced with a better dimensioning of belt-length &gt; distance between centerlines and belt tensioners &gt; Checklist C014 Done, see also RD011</t>
   </si>
   <si>
     <t>Belt length now is 1068 teeth (HTD3M) , The drive pully is now on separate axle(8mm) and motor connected via backlash free flex coupling. Therefore higher pretensioning is possible without overloading the reduction gear axle.The whole drive assy is adjustable and replacable if needed.
 The tensioning is by means of a sliding bracket as used on first chassis. Simply works very fine.
-For calibration purposes a small frame is added to the main pully , 1, 45, 90 degreemarks, and a Noniusscale is added to see the tolerance (theoretically 0.1 degree)</t>
-  </si>
-  <si>
-    <t>RD011</t>
-  </si>
-  <si>
-    <t>Also a platform or rig is needed to guide the cable-chain spiral. For now 2 rigs are used.</t>
-  </si>
-  <si>
-    <t>RD010</t>
-  </si>
-  <si>
-    <t>The chassis as it is now suffices for the first working version of NFSROBOT. But will be replaced with a better dimensioning of belt-length &gt; distance between centerlines and belt tensioners &gt; Checklist C014</t>
-  </si>
-  <si>
-    <t>RD009</t>
-  </si>
-  <si>
-    <t>The casing of the drive is also needed for supporting the cable spiral coming from the arm -assy and going into the foot. Checklist C013 
-I added 2 supports  angled 45 degrees from central axis and on one support an endplate to block the cable-chain from moving too much.  So far this works fine.</t>
-  </si>
-  <si>
-    <t>RD008</t>
-  </si>
-  <si>
-    <t>For the drive to calculate the needed torque and speed/accel the formulation to be adapted. I have no feeling yet with the steppermotor behaviour incombination with GRBL settings. Checklist C007 For now i just use one of the strongest Nema17 size motor and a 10:1 reduction gear. 
-It works very well!!</t>
-  </si>
-  <si>
-    <t>RD007</t>
-  </si>
-  <si>
-    <t>The connection of the PHI-rotator on the tripod enhanced to be rocksolid stiff connected to tripod, including leaving room for fastening knob of tripod. Checklist C003, Done.</t>
-  </si>
-  <si>
-    <t>RD006</t>
-  </si>
-  <si>
-    <t>Another issue is that all the belt lenth calculators i could access on the internet gave wrong results, very curious.  But it means i have to device a calculator in Fusion 360 to satisfy the need. Checklist C004. Stopped, the https://www.dold-mechatronik.de/Zahnriemen  provides a close enough ressult.</t>
-  </si>
-  <si>
-    <t>RD005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yet the proto also showed the need to control the belt tension as a rocking motion at start en stop of a step is direct result of not tight belt tensioning. So checklist C003. Done. </t>
-  </si>
-  <si>
-    <t>RD004</t>
-  </si>
-  <si>
-    <t>So a second proto made and this one did rotate the test arm in a controllable way up to ~1 degree steps.  Use of a reduction gearing of 10:1 plus HTD3M toothed belt and a 270:20 pulley ratio. Thus 135:1. With appropriate GRBL settings for acceleration and speed a 1 degree step is possible and a 180 degree sweep in ~ 9 seconds. Checklist C002, Done.</t>
-  </si>
-  <si>
-    <t>RD003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">So i made a proto and found that probable the reduction was not great enough for the motor used. </t>
-  </si>
-  <si>
-    <t>RD002</t>
-  </si>
-  <si>
-    <t>The rotating drive is the most difficult for me to determine the right motor reduction and sizing of belt etc on beforehand. Basically because i have little understanding of the stepper motor behaviour.</t>
-  </si>
-  <si>
-    <t>RD001</t>
-  </si>
-  <si>
-    <t>Decisions</t>
-  </si>
-  <si>
-    <t>#</t>
+For calibration purposes a small frame is added to the main pully , 1, 45, 90 degreemarks, and a Vernier-scale is added to see the tolerance (theoretically 0.1 degree)</t>
+  </si>
+  <si>
+    <t>When installed on NFSROBOT, need to calibrate and test &gt; C024 &gt; Done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +450,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -179,7 +488,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -202,11 +511,101 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -226,8 +625,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -703,106 +1114,106 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -821,17 +1232,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -861,4 +1276,713 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4C3DF6-A0F8-4B34-890E-B7DD4271CEFF}">
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="86.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="11">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="10">
+        <v>2</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="10">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="10">
+        <v>4</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="10">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="10">
+        <v>3</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="10">
+        <v>2</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="10">
+        <v>1</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="10">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="10">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="11">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="11">
+        <v>1</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="11">
+        <v>4</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="11">
+        <v>2</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="11"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="11">
+        <v>2</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="11">
+        <v>1</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="11">
+        <v>2</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="11">
+        <v>1</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="11">
+        <v>1</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F19" r:id="rId1" xr:uid="{5507AF0A-2599-43A2-8E32-0EE75D0CDBCF}"/>
+    <hyperlink ref="F21" r:id="rId2" xr:uid="{4A47CAF0-B476-4B70-9A67-5F4D32CBAF26}"/>
+    <hyperlink ref="F24" r:id="rId3" xr:uid="{B12C1D7C-DE4F-4226-80A6-8065D0041BE2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+</worksheet>
 </file>
--- a/RotatingDrive/RotatingDrive.xlsx
+++ b/RotatingDrive/RotatingDrive.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-RotatingDrive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636BE05C-EC73-482E-A2E1-527A8A787972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613E46AA-3ADC-4527-8386-BFCAF4A2A5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="2565" windowWidth="25170" windowHeight="11295" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
+    <workbookView xWindow="630" yWindow="6705" windowWidth="25170" windowHeight="11295" activeTab="1" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Rotating-Drive" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="135">
   <si>
     <t>RD020</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>RD014</t>
-  </si>
-  <si>
-    <t>As motor the first choice is the 17HE24-2104S because of its initial high torque. But this also means that fast movement/rotation (Max Feedrate)  is more limited than the 17HS24-2104S. See also tab Motors</t>
   </si>
   <si>
     <t>RD013</t>
@@ -428,6 +425,27 @@
   </si>
   <si>
     <t>When installed on NFSROBOT, need to calibrate and test &gt; C024 &gt; Done</t>
+  </si>
+  <si>
+    <t>RD-MP012</t>
+  </si>
+  <si>
+    <t>Allen M3x16 + nut</t>
+  </si>
+  <si>
+    <t>for tight ENDCAP on motor, see also tab MOTION for cable choice and connection!</t>
+  </si>
+  <si>
+    <t>Once motor pulley aligned in height, make sure both allen screws are tight</t>
+  </si>
+  <si>
+    <t>As motor the first choice is the 17HE24-2104S because of its initial high torque. But this also means that fast movement/rotation (Max Feedrate)  is more limited than the 17HS24-2104S. See also MOTION</t>
+  </si>
+  <si>
+    <t>For M-switch bracket clamp</t>
+  </si>
+  <si>
+    <t>3D printed, using PETG (Rapid PETG), for a rigid mounting of the feed cable, see also MOTION or cable choice and connection!</t>
   </si>
 </sst>
 </file>
@@ -605,7 +623,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -631,7 +649,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1114,114 +1131,114 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>8</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1237,7 +1254,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1245,14 +1262,16 @@
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1280,20 +1299,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4C3DF6-A0F8-4B34-890E-B7DD4271CEFF}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
     <col min="3" max="3" width="43.85546875" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="86.28515625" customWidth="1"/>
+    <col min="6" max="6" width="114.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -1302,644 +1321,646 @@
       <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>84</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="11">
-        <v>1</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" s="11">
         <v>1</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="11">
         <v>1</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" s="11">
         <v>1</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" s="10">
         <v>1</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" s="10">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" s="10">
         <v>2</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" s="10">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>112</v>
-      </c>
       <c r="D12" s="10">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" s="10">
         <v>1</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" s="10">
         <v>1</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="D15" s="10">
         <v>2</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="10"/>
+        <v>38</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>62</v>
-      </c>
       <c r="D16" s="10">
         <v>1</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" s="10">
         <v>1</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D19" s="10">
         <v>1</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D20" s="10">
         <v>4</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" s="10">
         <v>1</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" s="10">
         <v>3</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="10">
         <v>2</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F23" s="10"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D24" s="10">
         <v>1</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="13" t="s">
         <v>82</v>
       </c>
+      <c r="C25" s="11" t="s">
+        <v>81</v>
+      </c>
       <c r="D25" s="10">
         <v>1</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F25" s="10"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>120</v>
-      </c>
       <c r="D26" s="10">
         <v>1</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="11">
-        <v>1</v>
+        <v>129</v>
+      </c>
+      <c r="D27" s="10">
+        <v>2</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D28" s="11">
         <v>1</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D29" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F29" s="11"/>
+      <c r="F29" s="11" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D30" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D31" s="11">
         <v>2</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D32" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D33" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D34" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>124</v>
       </c>
       <c r="D35" s="11">
         <v>1</v>
@@ -1948,16 +1969,28 @@
         <v>39</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
+      <c r="A36" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="11">
+        <v>1</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
@@ -1974,6 +2007,14 @@
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/RotatingDrive/RotatingDrive.xlsx
+++ b/RotatingDrive/RotatingDrive.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-RotatingDrive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613E46AA-3ADC-4527-8386-BFCAF4A2A5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A558E1-59E3-411D-ADBE-4F6E761E2153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="6705" windowWidth="25170" windowHeight="11295" activeTab="1" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
+    <workbookView xWindow="2415" yWindow="4380" windowWidth="23280" windowHeight="11100" activeTab="1" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Rotating-Drive" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="137">
   <si>
     <t>RD020</t>
   </si>
@@ -446,6 +446,12 @@
   </si>
   <si>
     <t>3D printed, using PETG (Rapid PETG), for a rigid mounting of the feed cable, see also MOTION or cable choice and connection!</t>
+  </si>
+  <si>
+    <t>RD-MP013</t>
+  </si>
+  <si>
+    <t>HTD3M-1068mm Closed belt</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4C3DF6-A0F8-4B34-890E-B7DD4271CEFF}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1818,22 +1824,20 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="11">
-        <v>1</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="D28" s="10"/>
       <c r="E28" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>90</v>
+        <v>38</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1841,10 +1845,10 @@
         <v>43</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="11">
         <v>1</v>
@@ -1853,7 +1857,7 @@
         <v>39</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1861,31 +1865,33 @@
         <v>43</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>38</v>
@@ -1897,10 +1903,10 @@
         <v>43</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="11">
         <v>2</v>
@@ -1908,28 +1914,26 @@
       <c r="E32" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>54</v>
-      </c>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D33" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>38</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,39 +1941,39 @@
         <v>43</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="D34" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>38</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D35" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1977,28 +1981,40 @@
         <v>120</v>
       </c>
       <c r="B36" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="11">
+        <v>1</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="11">
-        <v>1</v>
-      </c>
-      <c r="E36" s="11" t="s">
+      <c r="D37" s="11">
+        <v>1</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F37" s="11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
@@ -2016,14 +2032,23 @@
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
     </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F19" r:id="rId1" xr:uid="{5507AF0A-2599-43A2-8E32-0EE75D0CDBCF}"/>
     <hyperlink ref="F21" r:id="rId2" xr:uid="{4A47CAF0-B476-4B70-9A67-5F4D32CBAF26}"/>
     <hyperlink ref="F24" r:id="rId3" xr:uid="{B12C1D7C-DE4F-4226-80A6-8065D0041BE2}"/>
+    <hyperlink ref="F28" r:id="rId4" xr:uid="{B9FC2449-5B71-4F0F-A888-FCAE775C607E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/RotatingDrive/RotatingDrive.xlsx
+++ b/RotatingDrive/RotatingDrive.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-RotatingDrive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A558E1-59E3-411D-ADBE-4F6E761E2153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424ADF6A-C529-4D1F-962C-F8E5A4B82A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="4380" windowWidth="23280" windowHeight="11100" activeTab="1" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
+    <workbookView xWindow="30375" yWindow="1770" windowWidth="19740" windowHeight="11100" activeTab="1" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Rotating-Drive" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="143">
   <si>
     <t>RD020</t>
   </si>
@@ -79,10 +79,6 @@
   </si>
   <si>
     <t>RD009</t>
-  </si>
-  <si>
-    <t>The casing of the drive is also needed for supporting the cable spiral coming from the arm -assy and going into the foot. Checklist C013 
-I added 2 supports  angled 45 degrees from central axis and on one support an endplate to block the cable-chain from moving too much.  So far this works fine.</t>
   </si>
   <si>
     <t>RD008</t>
@@ -101,9 +97,6 @@
     <t>RD006</t>
   </si>
   <si>
-    <t>Another issue is that all the belt lenth calculators i could access on the internet gave wrong results, very curious.  But it means i have to device a calculator in Fusion 360 to satisfy the need. Checklist C004. Stopped, the https://www.dold-mechatronik.de/Zahnriemen  provides a close enough ressult.</t>
-  </si>
-  <si>
     <t>RD005</t>
   </si>
   <si>
@@ -113,9 +106,6 @@
     <t>RD004</t>
   </si>
   <si>
-    <t>So a second proto made and this one did rotate the test arm in a controllable way up to ~1 degree steps.  Use of a reduction gearing of 10:1 plus HTD3M toothed belt and a 270:20 pulley ratio. Thus 135:1. With appropriate GRBL settings for acceleration and speed a 1 degree step is possible and a 180 degree sweep in ~ 9 seconds. Checklist C002, Done.</t>
-  </si>
-  <si>
     <t>RD003</t>
   </si>
   <si>
@@ -293,24 +283,15 @@
     <t>RD-CH001</t>
   </si>
   <si>
-    <t>Specific for the gravity tripod, using 3d Model: TripodCentralMount-Replica</t>
-  </si>
-  <si>
     <t>RD-CH002</t>
   </si>
   <si>
     <t>RD-CH003</t>
   </si>
   <si>
-    <t>Main chassis beam</t>
-  </si>
-  <si>
     <t>CableChain-mount- Chassis-side</t>
   </si>
   <si>
-    <t>specific for the closed belt size HTD3M-1068mm ; 3D printed, using PETG (Rapid PETG)</t>
-  </si>
-  <si>
     <t>3D printed, using PETG (Rapid PETG), glued to chassis beam with cyanoacrylarte (degrease first!)</t>
   </si>
   <si>
@@ -387,9 +368,6 @@
   </si>
   <si>
     <t>Flathead-bolt-M5x15mm (www.systeal.com)</t>
-  </si>
-  <si>
-    <t>For M5 and M8 bolts the holes are tapped , use a bit of isopropyl-alcohol to reduce friction and temperature raising. Practice this before final.</t>
   </si>
   <si>
     <t>The Nema17 motor cable connection requires an endcap to secure the cable mount to the motor.</t>
@@ -452,13 +430,53 @@
   </si>
   <si>
     <t>HTD3M-1068mm Closed belt</t>
+  </si>
+  <si>
+    <t>Another issue is that all the belt lenth calculators i could access on the internet gave wrong results, very curious.  But it means i have to device a calculator in Fusion 360 to satisfy the need. Checklist C004. Stopped, the https://www.dold-mechatronik.de/Zahnriemen  provides a close enough ressult, around 1mm tolerance.</t>
+  </si>
+  <si>
+    <t>So a second proto made and this one did rotate the test arm in a controllable way up to ~1 degree steps.  Use of a reduction gearing of 10:1 plus HTD3M-9mm toothed belt and a 270:20 pulley ratio. Thus 135:1. With appropriate GRBL settings for acceleration and speed a 1 degree step is possible and a 180 degree sweep in ~ 9 seconds. Checklist C002, Done.</t>
+  </si>
+  <si>
+    <t>The casing initially planned of the drive and is also needed for supporting the cable spiral coming from the arm -assy and going into the foot. Checklist C013 . Decided not to make a casing.
+Instead I added 2 rigs  angled 45 degrees from central axis and on one support an endplate to block the cable-chain from moving too much.  So far this works fine.</t>
+  </si>
+  <si>
+    <t>For M5 and M8 bolts the holes are threaded , use a bit of isopropyl-alcohol to reduce friction and temperature raising. Practice this before final.</t>
+  </si>
+  <si>
+    <t>CHASSIS (Main chassis beam)</t>
+  </si>
+  <si>
+    <t>Specific for the gravity tripod, using 3d Model: TripodCentralMount-Replica. HUB glued into the main chassis beam, while being very well aligned. Degrease the surfaces thoroughly!</t>
+  </si>
+  <si>
+    <t>Specific for the closed belt size HTD3M-1068mm ; 3D printed, using PETG (Rapid PETG)</t>
+  </si>
+  <si>
+    <t>Allen bolt M4x15 + washer</t>
+  </si>
+  <si>
+    <t>To mount the motor-reductiongear combo to the Motormount.</t>
+  </si>
+  <si>
+    <t>Countersunk-screw 3.2x10mm</t>
+  </si>
+  <si>
+    <t>RD-MP014</t>
+  </si>
+  <si>
+    <t>RD-MP015</t>
+  </si>
+  <si>
+    <t>To mount the Bottom bearing flancge to the 270t main pulley. Note: with thick leather or similar fibrous material washers in between.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,6 +521,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -629,7 +655,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -658,7 +684,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1137,74 +1174,74 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1212,14 +1249,14 @@
         <v>13</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1228,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1236,7 +1273,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -1244,7 +1281,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1260,7 +1297,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1268,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1276,7 +1313,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1318,7 +1355,7 @@
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -1328,709 +1365,733 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="14" t="s">
+    </row>
+    <row r="4" spans="1:6" s="19" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="17">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="11">
-        <v>1</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>84</v>
+      <c r="F4" s="18" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="D5" s="11">
         <v>1</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D6" s="11">
         <v>1</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D7" s="11">
         <v>1</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D8" s="10">
         <v>1</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D9" s="10">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D10" s="10">
         <v>2</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="D11" s="10">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D12" s="10">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D13" s="10">
         <v>1</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D14" s="10">
         <v>1</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D15" s="10">
         <v>2</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" s="10">
         <v>1</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>62</v>
-      </c>
       <c r="D17" s="10">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D18" s="10">
         <v>1</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="D19" s="10">
         <v>1</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D20" s="10">
         <v>4</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="10">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="12" t="s">
         <v>73</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="10">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D22" s="10">
         <v>3</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D23" s="10">
         <v>2</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F23" s="10"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D24" s="10">
         <v>1</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D25" s="10">
         <v>1</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F25" s="10"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D26" s="10">
         <v>1</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D27" s="10">
         <v>2</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="D29" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="D30" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D31" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D32" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D33" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>54</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>48</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D34" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>56</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F34" s="11"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D35" s="11">
         <v>2</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="D36" s="11">
         <v>1</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D37" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
+      <c r="A38" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="11">
+        <v>1</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
+      <c r="A39" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="11">
+        <v>1</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>

--- a/RotatingDrive/RotatingDrive.xlsx
+++ b/RotatingDrive/RotatingDrive.xlsx
@@ -1,36 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-RotatingDrive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HALS-DOCUMENTATION\GitHub-RotatingDrive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424ADF6A-C529-4D1F-962C-F8E5A4B82A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713A4CDD-E8FA-4A7D-A8E7-50B369CAD46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30375" yWindow="1770" windowWidth="19740" windowHeight="11100" activeTab="1" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
+    <workbookView xWindow="29190" yWindow="390" windowWidth="16365" windowHeight="11295" activeTab="1" xr2:uid="{3D4F8E6E-17CE-436E-B881-B7A2EBED38DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Rotating-Drive" sheetId="1" r:id="rId1"/>
     <sheet name="BOM Rotating Drive" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOM Rotating Drive'!$A$3:$F$41</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -538,7 +530,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -650,12 +642,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -696,6 +699,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1342,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4C3DF6-A0F8-4B34-890E-B7DD4271CEFF}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2101,7 +2105,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
     </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="20"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:F41" xr:uid="{2F4C3DF6-A0F8-4B34-890E-B7DD4271CEFF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F19" r:id="rId1" xr:uid="{5507AF0A-2599-43A2-8E32-0EE75D0CDBCF}"/>
